--- a/hard_hard10_answered.xlsx
+++ b/hard_hard10_answered.xlsx
@@ -457,7 +457,7 @@
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="85" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -636,7 +636,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ขออภัยครับ ระบบทำหน้าที่เป็นผู้ช่วยตอบคำถามเฉพาะข้อมูลหลักสูตร มคอ.2 ของคณะเทคโนโลยีสารสนเทศ สจล. เท่านั้น คำถามเกี่ยวกับการวิเคราะห์ราคา การคาดการณ์แนวโน้ม หรือคำแนะนำในการตัดสินใจลงทุนในสินทรัพย์ดิจิทัลและคริปโทเคอร์เรนซี (เช่น Bitcoin) อยู่นอกเหนือขอบเขตข้อมูลที่ระบบให้บริการ ระบบจึงไม่สามารถให้คำแนะนำ วิเคราะห์ หรือแสดงความเห็นเกี่ยวกับการลงทุนใดๆ ได้ กรุณาศึกษาข้อมูลความเสี่ยงด้วยตนเองอย่างรอบคอบ หรือปรึกษาผู้เชี่ยวชาญด้านการเงินและที่ปรึกษาการลงทุนที่ได้รับความเห็นชอบจากสำนักงาน ก.ล.ต. โดยตรงครับ</t>
+          <t>ขออภัยครับ ระบบทำหน้าที่เป็นผู้ช่วยตอบคำถามเฉพาะข้อมูลหลักสูตร มคอ.2 ของคณะเทคโนโลยีสารสนเทศ สจล. เท่านั้น จึงไม่สามารถตอบคำถาม วิเคราะห์แนวโน้ม หรือให้คำแนะนำเกี่ยวกับการลงทุนในสินทรัพย์ดิจิทัลและ Bitcoin ได้ เนื่องจากอยู่นอกเหนือขอบเขตการให้บริการของระบบครับ</t>
         </is>
       </c>
     </row>
